--- a/datasets/day1_excel_foundations/01_interface_and_workbook_basics/practice_completed.xlsx
+++ b/datasets/day1_excel_foundations/01_interface_and_workbook_basics/practice_completed.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
